--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -59,6 +59,9 @@
     <t>Nombre</t>
   </si>
   <si>
+    <t>ALCANTARA GUZMAN ANGEL DAVID</t>
+  </si>
+  <si>
     <t>ANDRES CORDOVA DAVID</t>
   </si>
   <si>
@@ -209,12 +212,12 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
@@ -231,6 +234,15 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>PAZ</t>
@@ -691,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -835,25 +847,25 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -898,25 +910,25 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -924,25 +936,25 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -987,25 +999,25 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1013,88 +1025,88 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>-1</v>
+      </c>
+      <c r="J6">
+        <v>-1</v>
+      </c>
+      <c r="K6">
+        <v>-1</v>
+      </c>
+      <c r="L6">
+        <v>-1</v>
+      </c>
+      <c r="M6">
+        <v>-1</v>
+      </c>
+      <c r="N6">
+        <v>-1</v>
+      </c>
+      <c r="O6">
+        <v>-1</v>
+      </c>
+      <c r="P6">
+        <v>-1</v>
+      </c>
+      <c r="Q6">
+        <v>-1</v>
+      </c>
+      <c r="R6">
+        <v>-1</v>
+      </c>
+      <c r="S6">
+        <v>-1</v>
+      </c>
+      <c r="T6">
+        <v>-1</v>
+      </c>
+      <c r="U6">
+        <v>-1</v>
+      </c>
+      <c r="V6">
+        <v>-1</v>
+      </c>
+      <c r="W6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>-1</v>
-      </c>
-      <c r="J6">
-        <v>-1</v>
-      </c>
-      <c r="K6">
-        <v>-1</v>
-      </c>
-      <c r="L6">
-        <v>-1</v>
-      </c>
-      <c r="M6">
-        <v>-1</v>
-      </c>
-      <c r="N6">
-        <v>-1</v>
-      </c>
-      <c r="O6">
-        <v>-1</v>
-      </c>
-      <c r="P6">
-        <v>-1</v>
-      </c>
-      <c r="Q6">
-        <v>-1</v>
-      </c>
-      <c r="R6">
-        <v>-1</v>
-      </c>
-      <c r="S6">
-        <v>-1</v>
-      </c>
-      <c r="T6">
-        <v>-1</v>
-      </c>
-      <c r="U6">
-        <v>-1</v>
-      </c>
-      <c r="V6">
-        <v>-1</v>
-      </c>
-      <c r="W6">
-        <v>9</v>
-      </c>
       <c r="X6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1102,26 +1114,26 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
       <c r="I7">
         <v>-1</v>
       </c>
@@ -1165,25 +1177,25 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z7">
+        <v>9</v>
+      </c>
+      <c r="AA7">
+        <v>6</v>
+      </c>
+      <c r="AB7">
+        <v>10</v>
+      </c>
+      <c r="AC7">
         <v>7</v>
-      </c>
-      <c r="AA7">
-        <v>5</v>
-      </c>
-      <c r="AB7">
-        <v>5</v>
-      </c>
-      <c r="AC7">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1191,22 +1203,22 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>4</v>
@@ -1254,22 +1266,22 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1280,25 +1292,25 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1343,25 +1355,25 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1369,25 +1381,25 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>10</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1432,25 +1444,25 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB10">
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1458,13 +1470,13 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -1476,7 +1488,7 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1521,13 +1533,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1539,7 +1551,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1547,13 +1559,13 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -1565,7 +1577,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1610,13 +1622,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1628,7 +1640,7 @@
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1636,25 +1648,25 @@
         <v>22</v>
       </c>
       <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
         <v>7</v>
       </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
-      <c r="D13">
-        <v>6</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
       <c r="G13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1699,25 +1711,25 @@
         <v>-1</v>
       </c>
       <c r="W13">
+        <v>8</v>
+      </c>
+      <c r="X13">
+        <v>6</v>
+      </c>
+      <c r="Y13">
+        <v>8</v>
+      </c>
+      <c r="Z13">
+        <v>9</v>
+      </c>
+      <c r="AA13">
         <v>7</v>
       </c>
-      <c r="X13">
-        <v>6</v>
-      </c>
-      <c r="Y13">
-        <v>6</v>
-      </c>
-      <c r="Z13">
-        <v>8</v>
-      </c>
-      <c r="AA13">
-        <v>5</v>
-      </c>
       <c r="AB13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1725,85 +1737,85 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>8</v>
+      </c>
+      <c r="I14">
+        <v>-1</v>
+      </c>
+      <c r="J14">
+        <v>-1</v>
+      </c>
+      <c r="K14">
+        <v>-1</v>
+      </c>
+      <c r="L14">
+        <v>-1</v>
+      </c>
+      <c r="M14">
+        <v>-1</v>
+      </c>
+      <c r="N14">
+        <v>-1</v>
+      </c>
+      <c r="O14">
+        <v>-1</v>
+      </c>
+      <c r="P14">
+        <v>-1</v>
+      </c>
+      <c r="Q14">
+        <v>-1</v>
+      </c>
+      <c r="R14">
+        <v>-1</v>
+      </c>
+      <c r="S14">
+        <v>-1</v>
+      </c>
+      <c r="T14">
+        <v>-1</v>
+      </c>
+      <c r="U14">
+        <v>-1</v>
+      </c>
+      <c r="V14">
+        <v>-1</v>
+      </c>
+      <c r="W14">
         <v>7</v>
       </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
-      <c r="H14">
-        <v>8</v>
-      </c>
-      <c r="I14">
-        <v>-1</v>
-      </c>
-      <c r="J14">
-        <v>-1</v>
-      </c>
-      <c r="K14">
-        <v>-1</v>
-      </c>
-      <c r="L14">
-        <v>-1</v>
-      </c>
-      <c r="M14">
-        <v>-1</v>
-      </c>
-      <c r="N14">
-        <v>-1</v>
-      </c>
-      <c r="O14">
-        <v>-1</v>
-      </c>
-      <c r="P14">
-        <v>-1</v>
-      </c>
-      <c r="Q14">
-        <v>-1</v>
-      </c>
-      <c r="R14">
-        <v>-1</v>
-      </c>
-      <c r="S14">
-        <v>-1</v>
-      </c>
-      <c r="T14">
-        <v>-1</v>
-      </c>
-      <c r="U14">
-        <v>-1</v>
-      </c>
-      <c r="V14">
-        <v>-1</v>
-      </c>
-      <c r="W14">
-        <v>9</v>
-      </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1814,88 +1826,88 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>-1</v>
+      </c>
+      <c r="J15">
+        <v>-1</v>
+      </c>
+      <c r="K15">
+        <v>-1</v>
+      </c>
+      <c r="L15">
+        <v>-1</v>
+      </c>
+      <c r="M15">
+        <v>-1</v>
+      </c>
+      <c r="N15">
+        <v>-1</v>
+      </c>
+      <c r="O15">
+        <v>-1</v>
+      </c>
+      <c r="P15">
+        <v>-1</v>
+      </c>
+      <c r="Q15">
+        <v>-1</v>
+      </c>
+      <c r="R15">
+        <v>-1</v>
+      </c>
+      <c r="S15">
+        <v>-1</v>
+      </c>
+      <c r="T15">
+        <v>-1</v>
+      </c>
+      <c r="U15">
+        <v>-1</v>
+      </c>
+      <c r="V15">
+        <v>-1</v>
+      </c>
+      <c r="W15">
+        <v>9</v>
+      </c>
+      <c r="X15">
+        <v>6</v>
+      </c>
+      <c r="Y15">
+        <v>9</v>
+      </c>
+      <c r="Z15">
+        <v>9</v>
+      </c>
+      <c r="AA15">
         <v>7</v>
       </c>
-      <c r="I15">
-        <v>-1</v>
-      </c>
-      <c r="J15">
-        <v>-1</v>
-      </c>
-      <c r="K15">
-        <v>-1</v>
-      </c>
-      <c r="L15">
-        <v>-1</v>
-      </c>
-      <c r="M15">
-        <v>-1</v>
-      </c>
-      <c r="N15">
-        <v>-1</v>
-      </c>
-      <c r="O15">
-        <v>-1</v>
-      </c>
-      <c r="P15">
-        <v>-1</v>
-      </c>
-      <c r="Q15">
-        <v>-1</v>
-      </c>
-      <c r="R15">
-        <v>-1</v>
-      </c>
-      <c r="S15">
-        <v>-1</v>
-      </c>
-      <c r="T15">
-        <v>-1</v>
-      </c>
-      <c r="U15">
-        <v>-1</v>
-      </c>
-      <c r="V15">
-        <v>-1</v>
-      </c>
-      <c r="W15">
-        <v>6</v>
-      </c>
-      <c r="X15">
-        <v>5</v>
-      </c>
-      <c r="Y15">
-        <v>6</v>
-      </c>
-      <c r="Z15">
-        <v>5</v>
-      </c>
-      <c r="AA15">
-        <v>5</v>
-      </c>
       <c r="AB15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1903,26 +1915,26 @@
         <v>25</v>
       </c>
       <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
         <v>7</v>
       </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
-      <c r="D16">
-        <v>6</v>
-      </c>
-      <c r="E16">
-        <v>8</v>
-      </c>
-      <c r="F16">
-        <v>5</v>
-      </c>
-      <c r="G16">
-        <v>9</v>
-      </c>
-      <c r="H16">
-        <v>6</v>
-      </c>
       <c r="I16">
         <v>-1</v>
       </c>
@@ -1966,25 +1978,25 @@
         <v>-1</v>
       </c>
       <c r="W16">
+        <v>6</v>
+      </c>
+      <c r="X16">
+        <v>5</v>
+      </c>
+      <c r="Y16">
+        <v>6</v>
+      </c>
+      <c r="Z16">
+        <v>5</v>
+      </c>
+      <c r="AA16">
+        <v>5</v>
+      </c>
+      <c r="AB16">
+        <v>9</v>
+      </c>
+      <c r="AC16">
         <v>7</v>
-      </c>
-      <c r="X16">
-        <v>6</v>
-      </c>
-      <c r="Y16">
-        <v>6</v>
-      </c>
-      <c r="Z16">
-        <v>8</v>
-      </c>
-      <c r="AA16">
-        <v>5</v>
-      </c>
-      <c r="AB16">
-        <v>9</v>
-      </c>
-      <c r="AC16">
-        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1992,25 +2004,25 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2055,25 +2067,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>5</v>
       </c>
       <c r="AB17">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2081,25 +2093,25 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2144,25 +2156,25 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2176,19 +2188,19 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19">
         <v>9</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <v>10</v>
       </c>
       <c r="H19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2239,19 +2251,19 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2262,22 +2274,22 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>8</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2325,22 +2337,22 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>8</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2351,22 +2363,22 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2414,22 +2426,22 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2443,16 +2455,16 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>8</v>
@@ -2506,16 +2518,16 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2526,22 +2538,22 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>9</v>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23">
         <v>8</v>
@@ -2589,22 +2601,22 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2618,22 +2630,22 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>10</v>
       </c>
       <c r="H24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2681,22 +2693,22 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2704,16 +2716,16 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -2722,7 +2734,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2767,16 +2779,16 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2785,7 +2797,7 @@
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2793,88 +2805,88 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+      <c r="H26">
+        <v>9</v>
+      </c>
+      <c r="I26">
+        <v>-1</v>
+      </c>
+      <c r="J26">
+        <v>-1</v>
+      </c>
+      <c r="K26">
+        <v>-1</v>
+      </c>
+      <c r="L26">
+        <v>-1</v>
+      </c>
+      <c r="M26">
+        <v>-1</v>
+      </c>
+      <c r="N26">
+        <v>-1</v>
+      </c>
+      <c r="O26">
+        <v>-1</v>
+      </c>
+      <c r="P26">
+        <v>-1</v>
+      </c>
+      <c r="Q26">
+        <v>-1</v>
+      </c>
+      <c r="R26">
+        <v>-1</v>
+      </c>
+      <c r="S26">
+        <v>-1</v>
+      </c>
+      <c r="T26">
+        <v>-1</v>
+      </c>
+      <c r="U26">
+        <v>-1</v>
+      </c>
+      <c r="V26">
+        <v>-1</v>
+      </c>
+      <c r="W26">
+        <v>8</v>
+      </c>
+      <c r="X26">
         <v>7</v>
       </c>
-      <c r="F26">
-        <v>5</v>
-      </c>
-      <c r="G26">
-        <v>8</v>
-      </c>
-      <c r="H26">
-        <v>7</v>
-      </c>
-      <c r="I26">
-        <v>-1</v>
-      </c>
-      <c r="J26">
-        <v>-1</v>
-      </c>
-      <c r="K26">
-        <v>-1</v>
-      </c>
-      <c r="L26">
-        <v>-1</v>
-      </c>
-      <c r="M26">
-        <v>-1</v>
-      </c>
-      <c r="N26">
-        <v>-1</v>
-      </c>
-      <c r="O26">
-        <v>-1</v>
-      </c>
-      <c r="P26">
-        <v>-1</v>
-      </c>
-      <c r="Q26">
-        <v>-1</v>
-      </c>
-      <c r="R26">
-        <v>-1</v>
-      </c>
-      <c r="S26">
-        <v>-1</v>
-      </c>
-      <c r="T26">
-        <v>-1</v>
-      </c>
-      <c r="U26">
-        <v>-1</v>
-      </c>
-      <c r="V26">
-        <v>-1</v>
-      </c>
-      <c r="W26">
-        <v>6</v>
-      </c>
-      <c r="X26">
-        <v>5</v>
-      </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2882,25 +2894,25 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2945,25 +2957,25 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2971,16 +2983,16 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -2989,7 +3001,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3034,16 +3046,16 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -3052,7 +3064,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3060,25 +3072,25 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3123,25 +3135,25 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB29">
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3149,19 +3161,19 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30">
         <v>8</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G30">
         <v>10</v>
@@ -3212,19 +3224,19 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3238,19 +3250,19 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>8</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31">
         <v>10</v>
@@ -3301,19 +3313,19 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z31">
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3327,25 +3339,25 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G32">
         <v>10</v>
       </c>
       <c r="H32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3390,25 +3402,25 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>10</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3416,16 +3428,16 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F33">
         <v>5</v>
@@ -3434,7 +3446,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3479,16 +3491,16 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>5</v>
@@ -3497,7 +3509,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3505,22 +3517,22 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F34">
         <v>5</v>
       </c>
       <c r="G34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H34">
         <v>6</v>
@@ -3568,22 +3580,22 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA34">
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC34">
         <v>6</v>
@@ -3594,16 +3606,16 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -3612,7 +3624,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3657,16 +3669,16 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y35">
         <v>5</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>5</v>
@@ -3675,7 +3687,7 @@
         <v>9</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3683,22 +3695,22 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H36">
         <v>10</v>
@@ -3746,22 +3758,22 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC36">
         <v>10</v>
@@ -3772,87 +3784,176 @@
         <v>46</v>
       </c>
       <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37">
+        <v>10</v>
+      </c>
+      <c r="I37">
+        <v>-1</v>
+      </c>
+      <c r="J37">
+        <v>-1</v>
+      </c>
+      <c r="K37">
+        <v>-1</v>
+      </c>
+      <c r="L37">
+        <v>-1</v>
+      </c>
+      <c r="M37">
+        <v>-1</v>
+      </c>
+      <c r="N37">
+        <v>-1</v>
+      </c>
+      <c r="O37">
+        <v>-1</v>
+      </c>
+      <c r="P37">
+        <v>-1</v>
+      </c>
+      <c r="Q37">
+        <v>-1</v>
+      </c>
+      <c r="R37">
+        <v>-1</v>
+      </c>
+      <c r="S37">
+        <v>-1</v>
+      </c>
+      <c r="T37">
+        <v>-1</v>
+      </c>
+      <c r="U37">
+        <v>-1</v>
+      </c>
+      <c r="V37">
+        <v>-1</v>
+      </c>
+      <c r="W37">
+        <v>10</v>
+      </c>
+      <c r="X37">
+        <v>9</v>
+      </c>
+      <c r="Y37">
+        <v>10</v>
+      </c>
+      <c r="Z37">
+        <v>10</v>
+      </c>
+      <c r="AA37">
+        <v>10</v>
+      </c>
+      <c r="AB37">
+        <v>10</v>
+      </c>
+      <c r="AC37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38">
         <v>4</v>
       </c>
-      <c r="C37">
-        <v>5</v>
-      </c>
-      <c r="D37">
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
         <v>0</v>
       </c>
-      <c r="E37">
-        <v>5</v>
-      </c>
-      <c r="F37">
-        <v>5</v>
-      </c>
-      <c r="G37">
-        <v>5</v>
-      </c>
-      <c r="H37">
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="H38">
         <v>4</v>
       </c>
-      <c r="I37">
-        <v>-1</v>
-      </c>
-      <c r="J37">
-        <v>-1</v>
-      </c>
-      <c r="K37">
-        <v>-1</v>
-      </c>
-      <c r="L37">
-        <v>-1</v>
-      </c>
-      <c r="M37">
-        <v>-1</v>
-      </c>
-      <c r="N37">
-        <v>-1</v>
-      </c>
-      <c r="O37">
-        <v>-1</v>
-      </c>
-      <c r="P37">
-        <v>-1</v>
-      </c>
-      <c r="Q37">
-        <v>-1</v>
-      </c>
-      <c r="R37">
-        <v>-1</v>
-      </c>
-      <c r="S37">
-        <v>-1</v>
-      </c>
-      <c r="T37">
-        <v>-1</v>
-      </c>
-      <c r="U37">
-        <v>-1</v>
-      </c>
-      <c r="V37">
-        <v>-1</v>
-      </c>
-      <c r="W37">
-        <v>5</v>
-      </c>
-      <c r="X37">
-        <v>5</v>
-      </c>
-      <c r="Y37">
-        <v>5</v>
-      </c>
-      <c r="Z37">
-        <v>5</v>
-      </c>
-      <c r="AA37">
-        <v>5</v>
-      </c>
-      <c r="AB37">
-        <v>5</v>
-      </c>
-      <c r="AC37">
+      <c r="I38">
+        <v>-1</v>
+      </c>
+      <c r="J38">
+        <v>-1</v>
+      </c>
+      <c r="K38">
+        <v>-1</v>
+      </c>
+      <c r="L38">
+        <v>-1</v>
+      </c>
+      <c r="M38">
+        <v>-1</v>
+      </c>
+      <c r="N38">
+        <v>-1</v>
+      </c>
+      <c r="O38">
+        <v>-1</v>
+      </c>
+      <c r="P38">
+        <v>-1</v>
+      </c>
+      <c r="Q38">
+        <v>-1</v>
+      </c>
+      <c r="R38">
+        <v>-1</v>
+      </c>
+      <c r="S38">
+        <v>-1</v>
+      </c>
+      <c r="T38">
+        <v>-1</v>
+      </c>
+      <c r="U38">
+        <v>-1</v>
+      </c>
+      <c r="V38">
+        <v>-1</v>
+      </c>
+      <c r="W38">
+        <v>5</v>
+      </c>
+      <c r="X38">
+        <v>5</v>
+      </c>
+      <c r="Y38">
+        <v>5</v>
+      </c>
+      <c r="Z38">
+        <v>5</v>
+      </c>
+      <c r="AA38">
+        <v>5</v>
+      </c>
+      <c r="AB38">
+        <v>5</v>
+      </c>
+      <c r="AC38">
         <v>5</v>
       </c>
     </row>
@@ -3869,7 +3970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3878,7 +3979,7 @@
     <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3887,7 +3988,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3896,7 +3997,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -3983,67 +4084,67 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>90</v>
       </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>90</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
-      <c r="M4">
-        <v>100</v>
-      </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>90</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>100</v>
-      </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4051,13 +4152,13 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4066,19 +4167,19 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4087,19 +4188,19 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4108,7 +4209,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4119,13 +4220,13 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -4134,19 +4235,19 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
         <v>90</v>
       </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
       <c r="J6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4155,19 +4256,19 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>90</v>
       </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
       <c r="Q6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -4176,10 +4277,10 @@
         <v>100</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V6">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4187,13 +4288,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -4205,16 +4306,16 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4226,16 +4327,16 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4247,7 +4348,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4258,10 +4359,10 @@
         <v>80</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -4270,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -4279,10 +4380,10 @@
         <v>80</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -4291,7 +4392,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4300,10 +4401,10 @@
         <v>80</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4312,7 +4413,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4323,13 +4424,13 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -4338,19 +4439,19 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -4359,19 +4460,19 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4380,7 +4481,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -4397,7 +4498,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -4418,7 +4519,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4439,7 +4540,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4465,7 +4566,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -4486,7 +4587,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4507,7 +4608,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4533,7 +4634,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -4554,7 +4655,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4575,7 +4676,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4595,13 +4696,13 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4610,19 +4711,19 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -4631,19 +4732,19 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4652,7 +4753,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4663,13 +4764,13 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4678,19 +4779,19 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4699,19 +4800,19 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>78.3</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4720,7 +4821,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4731,19 +4832,19 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C15">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>100</v>
       </c>
       <c r="F15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -4752,19 +4853,19 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -4773,19 +4874,19 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4805,7 +4906,7 @@
         <v>93.3</v>
       </c>
       <c r="D16">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4826,7 +4927,7 @@
         <v>93.3</v>
       </c>
       <c r="K16">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4847,7 +4948,7 @@
         <v>93.3</v>
       </c>
       <c r="R16">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -4870,64 +4971,64 @@
         <v>80</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>93.3</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>80</v>
       </c>
       <c r="J17">
-        <v>20</v>
+        <v>93.3</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="P17">
         <v>80</v>
       </c>
       <c r="Q17">
-        <v>20</v>
+        <v>93.3</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>78.3</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4935,67 +5036,67 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5009,7 +5110,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -5030,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5051,7 +5152,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5077,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -5098,7 +5199,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5119,7 +5220,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5142,10 +5243,10 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D21">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -5157,16 +5258,16 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5178,16 +5279,16 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5199,7 +5300,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5210,10 +5311,10 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D22">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -5225,16 +5326,16 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I22">
         <v>100</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5246,16 +5347,16 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5267,7 +5368,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5278,10 +5379,10 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -5293,16 +5394,16 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5314,16 +5415,16 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5335,7 +5436,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5349,7 +5450,7 @@
         <v>80</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -5361,7 +5462,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -5370,7 +5471,7 @@
         <v>80</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5382,7 +5483,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5391,7 +5492,7 @@
         <v>80</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5403,7 +5504,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5411,13 +5512,13 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -5426,19 +5527,19 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>100</v>
       </c>
       <c r="I25">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -5447,19 +5548,19 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5468,7 +5569,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5479,13 +5580,13 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C26">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -5494,19 +5595,19 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
         <v>90</v>
       </c>
-      <c r="I26">
-        <v>80</v>
-      </c>
       <c r="J26">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -5515,19 +5616,19 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
         <v>90</v>
       </c>
-      <c r="P26">
-        <v>80</v>
-      </c>
       <c r="Q26">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5536,10 +5637,10 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V26">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5547,13 +5648,13 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -5565,16 +5666,16 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5586,16 +5687,16 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5607,7 +5708,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5615,13 +5716,13 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -5636,13 +5737,13 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5657,13 +5758,13 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5683,13 +5784,13 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -5704,13 +5805,13 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5725,13 +5826,13 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5757,7 +5858,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -5778,7 +5879,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5799,7 +5900,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5825,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -5846,7 +5947,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5867,7 +5968,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5887,16 +5988,16 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E32">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -5908,16 +6009,16 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L32">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -5929,16 +6030,16 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q32">
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S32">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -5961,10 +6062,10 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5982,10 +6083,10 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -6003,10 +6104,10 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="T33">
         <v>100</v>
@@ -6023,13 +6124,13 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -6038,19 +6139,19 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>100</v>
       </c>
       <c r="I34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -6059,19 +6160,19 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O34">
         <v>100</v>
       </c>
       <c r="P34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q34">
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -6080,7 +6181,7 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6091,13 +6192,13 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C35">
         <v>100</v>
       </c>
       <c r="D35">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -6112,13 +6213,13 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -6133,13 +6234,13 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6159,13 +6260,13 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C36">
         <v>100</v>
       </c>
       <c r="D36">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="E36">
         <v>100</v>
@@ -6174,19 +6275,19 @@
         <v>100</v>
       </c>
       <c r="G36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -6195,19 +6296,19 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6216,7 +6317,7 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6227,66 +6328,134 @@
         <v>46</v>
       </c>
       <c r="B37">
+        <v>100</v>
+      </c>
+      <c r="C37">
+        <v>100</v>
+      </c>
+      <c r="D37">
+        <v>87</v>
+      </c>
+      <c r="E37">
+        <v>100</v>
+      </c>
+      <c r="F37">
+        <v>100</v>
+      </c>
+      <c r="G37">
+        <v>100</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <v>100</v>
+      </c>
+      <c r="J37">
+        <v>100</v>
+      </c>
+      <c r="K37">
+        <v>87</v>
+      </c>
+      <c r="L37">
+        <v>100</v>
+      </c>
+      <c r="M37">
+        <v>100</v>
+      </c>
+      <c r="N37">
+        <v>100</v>
+      </c>
+      <c r="O37">
+        <v>100</v>
+      </c>
+      <c r="P37">
+        <v>100</v>
+      </c>
+      <c r="Q37">
+        <v>100</v>
+      </c>
+      <c r="R37">
+        <v>87</v>
+      </c>
+      <c r="S37">
+        <v>100</v>
+      </c>
+      <c r="T37">
+        <v>100</v>
+      </c>
+      <c r="U37">
+        <v>100</v>
+      </c>
+      <c r="V37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
+      <c r="A38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38">
         <v>80</v>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>60</v>
       </c>
-      <c r="D37">
-        <v>20</v>
-      </c>
-      <c r="E37">
+      <c r="D38">
+        <v>17.4</v>
+      </c>
+      <c r="E38">
         <v>40</v>
       </c>
-      <c r="F37">
+      <c r="F38">
         <v>0</v>
       </c>
-      <c r="G37">
+      <c r="G38">
         <v>25</v>
       </c>
-      <c r="H37">
+      <c r="H38">
         <v>60</v>
       </c>
-      <c r="I37">
+      <c r="I38">
         <v>80</v>
       </c>
-      <c r="J37">
+      <c r="J38">
         <v>60</v>
       </c>
-      <c r="K37">
-        <v>20</v>
-      </c>
-      <c r="L37">
+      <c r="K38">
+        <v>17.4</v>
+      </c>
+      <c r="L38">
         <v>40</v>
       </c>
-      <c r="M37">
+      <c r="M38">
         <v>0</v>
       </c>
-      <c r="N37">
+      <c r="N38">
         <v>25</v>
       </c>
-      <c r="O37">
+      <c r="O38">
         <v>60</v>
       </c>
-      <c r="P37">
+      <c r="P38">
         <v>80</v>
       </c>
-      <c r="Q37">
+      <c r="Q38">
         <v>60</v>
       </c>
-      <c r="R37">
-        <v>20</v>
-      </c>
-      <c r="S37">
+      <c r="R38">
+        <v>17.4</v>
+      </c>
+      <c r="S38">
         <v>40</v>
       </c>
-      <c r="T37">
+      <c r="T38">
         <v>0</v>
       </c>
-      <c r="U37">
+      <c r="U38">
         <v>25</v>
       </c>
-      <c r="V37">
+      <c r="V38">
         <v>60</v>
       </c>
     </row>
@@ -6315,31 +6484,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6347,22 +6516,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
         <v>14</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="G2" s="2">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -6379,22 +6548,22 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3">
         <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="G3" s="2">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="H3">
         <v>6.3</v>
@@ -6411,22 +6580,22 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="G4" s="2">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="H4">
         <v>7.4</v>
@@ -6440,60 +6609,60 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>11.8</v>
+        <v>8.6</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>31</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>91.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>8.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6504,28 +6673,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6539,25 +6708,25 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G8" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H8">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6568,10 +6737,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -6593,7 +6762,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6602,22 +6771,42 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>23330051920213</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6627,7 +6816,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6636,22 +6825,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6659,45 +6848,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920067</v>
+        <v>23330051920213</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920067</v>
+        <v>23330051920213</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6705,19 +6894,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920071</v>
+        <v>23330051920067</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
@@ -6728,22 +6917,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920071</v>
+        <v>23330051920067</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6751,22 +6940,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920072</v>
+        <v>23330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6774,22 +6963,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920072</v>
+        <v>23330051920071</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6797,19 +6986,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920074</v>
+        <v>23330051920072</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
@@ -6820,22 +7009,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920074</v>
+        <v>23330051920072</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6843,22 +7032,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920057</v>
+        <v>23330051920074</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6866,22 +7055,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920246</v>
+        <v>23330051920074</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6889,22 +7078,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920061</v>
+        <v>23330051920057</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6912,22 +7101,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920062</v>
+        <v>23330051920246</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6935,22 +7124,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920064</v>
+        <v>23330051920061</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6958,22 +7147,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920259</v>
+        <v>23330051920062</v>
       </c>
       <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
         <v>80</v>
       </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -6981,22 +7170,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920065</v>
+        <v>23330051920064</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7004,24 +7193,70 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
+        <v>23330051920259</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920065</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
         <v>23330051920066</v>
       </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17">
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>ALCANTARA GUZMAN ANGEL DAVID</t>
-  </si>
-  <si>
     <t>ANDRES CORDOVA DAVID</t>
   </si>
   <si>
@@ -206,21 +203,21 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -236,112 +233,49 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
   </si>
   <si>
     <t>XIMENA ANALY</t>
   </si>
   <si>
-    <t>IVONNE ERIMAR</t>
-  </si>
-  <si>
     <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
-    <t>CRIZULY AMITHAI</t>
-  </si>
-  <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
-    <t>REINA IVETT</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
-  </si>
-  <si>
-    <t>MELANIE YARETZI</t>
-  </si>
-  <si>
-    <t>DENISSE</t>
-  </si>
-  <si>
-    <t>YASMIN</t>
   </si>
 </sst>
 </file>
@@ -703,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -847,40 +781,40 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -910,25 +844,25 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -936,40 +870,40 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -999,25 +933,25 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1025,40 +959,40 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1088,25 +1022,25 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1114,40 +1048,40 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1177,25 +1111,25 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1203,40 +1137,40 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H8">
         <v>4</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1266,22 +1200,22 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>5</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1292,40 +1226,40 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1355,25 +1289,25 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1381,40 +1315,40 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>10</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1444,25 +1378,25 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1470,13 +1404,13 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -1488,22 +1422,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1533,13 +1467,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1551,7 +1485,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1559,13 +1493,13 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -1577,22 +1511,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1625,10 +1559,10 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1640,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1648,40 +1582,40 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1711,25 +1645,25 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1737,40 +1671,40 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H14">
         <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1800,22 +1734,22 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1826,40 +1760,40 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1889,25 +1823,25 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1915,16 +1849,16 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -1933,22 +1867,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1978,16 +1912,16 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -1996,7 +1930,7 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2004,40 +1938,40 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
       <c r="G17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2067,25 +2001,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>5</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2093,40 +2027,40 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2156,25 +2090,25 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2188,34 +2122,34 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>9</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>10</v>
       </c>
       <c r="H19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2245,25 +2179,25 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2274,37 +2208,37 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>8</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2334,25 +2268,25 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2363,37 +2297,37 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21">
         <v>8</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2423,25 +2357,25 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2455,34 +2389,34 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2512,22 +2446,22 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2538,40 +2472,40 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>9</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2601,22 +2535,22 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>8</v>
@@ -2630,37 +2564,37 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>10</v>
       </c>
       <c r="H24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2690,25 +2624,25 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2716,16 +2650,16 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -2734,22 +2668,22 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2782,13 +2716,13 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>5</v>
@@ -2797,7 +2731,7 @@
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2805,40 +2739,40 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>5</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2868,25 +2802,25 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2894,40 +2828,40 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
       <c r="G27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2957,25 +2891,25 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2983,16 +2917,16 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -3001,22 +2935,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3049,13 +2983,13 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA28">
         <v>5</v>
@@ -3064,7 +2998,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3072,40 +3006,40 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>10</v>
       </c>
       <c r="H29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3135,25 +3069,25 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3161,19 +3095,19 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>8</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>10</v>
@@ -3182,19 +3116,19 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3227,16 +3161,16 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3250,19 +3184,19 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31">
         <v>8</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>10</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>10</v>
@@ -3271,19 +3205,19 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3313,19 +3247,19 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z31">
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3339,40 +3273,40 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>10</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3402,25 +3336,25 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB32">
         <v>10</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3428,16 +3362,16 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F33">
         <v>5</v>
@@ -3446,22 +3380,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3491,16 +3425,16 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA33">
         <v>5</v>
@@ -3509,7 +3443,7 @@
         <v>10</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3517,40 +3451,40 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>5</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H34">
         <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3580,22 +3514,22 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z34">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AA34">
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC34">
         <v>6</v>
@@ -3606,16 +3540,16 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -3624,22 +3558,22 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3669,25 +3603,25 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB35">
         <v>9</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3695,40 +3629,40 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3758,22 +3692,22 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC36">
         <v>10</v>
@@ -3784,40 +3718,40 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H37">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3847,113 +3781,24 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC37">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29">
-      <c r="A38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38">
-        <v>4</v>
-      </c>
-      <c r="C38">
-        <v>5</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38">
-        <v>5</v>
-      </c>
-      <c r="F38">
-        <v>5</v>
-      </c>
-      <c r="G38">
-        <v>5</v>
-      </c>
-      <c r="H38">
-        <v>4</v>
-      </c>
-      <c r="I38">
-        <v>-1</v>
-      </c>
-      <c r="J38">
-        <v>-1</v>
-      </c>
-      <c r="K38">
-        <v>-1</v>
-      </c>
-      <c r="L38">
-        <v>-1</v>
-      </c>
-      <c r="M38">
-        <v>-1</v>
-      </c>
-      <c r="N38">
-        <v>-1</v>
-      </c>
-      <c r="O38">
-        <v>-1</v>
-      </c>
-      <c r="P38">
-        <v>-1</v>
-      </c>
-      <c r="Q38">
-        <v>-1</v>
-      </c>
-      <c r="R38">
-        <v>-1</v>
-      </c>
-      <c r="S38">
-        <v>-1</v>
-      </c>
-      <c r="T38">
-        <v>-1</v>
-      </c>
-      <c r="U38">
-        <v>-1</v>
-      </c>
-      <c r="V38">
-        <v>-1</v>
-      </c>
-      <c r="W38">
-        <v>5</v>
-      </c>
-      <c r="X38">
-        <v>5</v>
-      </c>
-      <c r="Y38">
-        <v>5</v>
-      </c>
-      <c r="Z38">
-        <v>5</v>
-      </c>
-      <c r="AA38">
-        <v>5</v>
-      </c>
-      <c r="AB38">
-        <v>5</v>
-      </c>
-      <c r="AC38">
         <v>5</v>
       </c>
     </row>
@@ -3970,7 +3815,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3979,7 +3824,7 @@
     <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3988,7 +3833,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -3997,7 +3842,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -4084,67 +3929,67 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -4152,13 +3997,13 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D5">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4167,19 +4012,19 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K5">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -4188,19 +4033,19 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4209,7 +4054,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4220,67 +4065,67 @@
         <v>15</v>
       </c>
       <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
         <v>90</v>
       </c>
-      <c r="C6">
-        <v>80</v>
-      </c>
-      <c r="D6">
-        <v>87</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>93.8</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
       <c r="I6">
+        <v>100</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>100</v>
+      </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
         <v>90</v>
       </c>
-      <c r="J6">
-        <v>80</v>
-      </c>
-      <c r="K6">
-        <v>87</v>
-      </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
-      <c r="M6">
-        <v>100</v>
-      </c>
-      <c r="N6">
-        <v>93.8</v>
-      </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
       <c r="P6">
+        <v>100</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
         <v>90</v>
-      </c>
-      <c r="Q6">
-        <v>80</v>
-      </c>
-      <c r="R6">
-        <v>87</v>
-      </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
-        <v>100</v>
-      </c>
-      <c r="U6">
-        <v>93.8</v>
-      </c>
-      <c r="V6">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4288,13 +4133,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D7">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -4306,16 +4151,16 @@
         <v>100</v>
       </c>
       <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
         <v>90</v>
       </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
       <c r="J7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K7">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -4327,16 +4172,16 @@
         <v>100</v>
       </c>
       <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
         <v>90</v>
       </c>
-      <c r="P7">
-        <v>100</v>
-      </c>
       <c r="Q7">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R7">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4348,7 +4193,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4359,10 +4204,10 @@
         <v>80</v>
       </c>
       <c r="C8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -4371,19 +4216,19 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -4392,19 +4237,19 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4413,7 +4258,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4424,13 +4269,13 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -4439,19 +4284,19 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -4460,19 +4305,19 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4481,7 +4326,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -4498,7 +4343,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -4519,7 +4364,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4540,7 +4385,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4566,7 +4411,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -4587,7 +4432,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4608,7 +4453,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4634,7 +4479,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -4655,7 +4500,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4676,7 +4521,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4696,13 +4541,13 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4711,49 +4556,49 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T13">
         <v>100</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4764,13 +4609,13 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4779,19 +4624,19 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4800,19 +4645,19 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>78.3</v>
+        <v>100</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4821,7 +4666,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4832,19 +4677,19 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="D15">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -4853,19 +4698,19 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="K15">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -4874,19 +4719,19 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="R15">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4906,7 +4751,7 @@
         <v>93.3</v>
       </c>
       <c r="D16">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4921,19 +4766,19 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J16">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="K16">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -4942,19 +4787,19 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q16">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R16">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4971,64 +4816,64 @@
         <v>80</v>
       </c>
       <c r="C17">
-        <v>93.3</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I17">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J17">
-        <v>93.3</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="P17">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q17">
-        <v>93.3</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>78.3</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5036,67 +4881,67 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C18">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="I18">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V18">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5110,7 +4955,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -5131,7 +4976,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5152,7 +4997,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5178,7 +5023,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -5199,7 +5044,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -5220,7 +5065,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5243,10 +5088,10 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D21">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -5258,16 +5103,16 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I21">
         <v>100</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K21">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5279,16 +5124,16 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R21">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5300,7 +5145,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5311,10 +5156,10 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -5326,16 +5171,16 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>100</v>
       </c>
       <c r="J22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5347,16 +5192,16 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5368,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5379,10 +5224,10 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D23">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -5394,16 +5239,16 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I23">
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K23">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -5415,16 +5260,16 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R23">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5436,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5450,7 +5295,7 @@
         <v>80</v>
       </c>
       <c r="D24">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -5462,16 +5307,16 @@
         <v>100</v>
       </c>
       <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>100</v>
+      </c>
+      <c r="J24">
         <v>90</v>
       </c>
-      <c r="I24">
-        <v>100</v>
-      </c>
-      <c r="J24">
-        <v>80</v>
-      </c>
       <c r="K24">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5483,16 +5328,16 @@
         <v>100</v>
       </c>
       <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
         <v>90</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>80</v>
-      </c>
       <c r="R24">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5504,7 +5349,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5512,13 +5357,13 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C25">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D25">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -5527,49 +5372,49 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H25">
         <v>100</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J25">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q25">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T25">
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5580,67 +5425,67 @@
         <v>35</v>
       </c>
       <c r="B26">
+        <v>80</v>
+      </c>
+      <c r="C26">
+        <v>80</v>
+      </c>
+      <c r="D26">
+        <v>100</v>
+      </c>
+      <c r="E26">
+        <v>100</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26">
         <v>90</v>
-      </c>
-      <c r="C26">
-        <v>100</v>
-      </c>
-      <c r="D26">
-        <v>87</v>
-      </c>
-      <c r="E26">
-        <v>100</v>
-      </c>
-      <c r="F26">
-        <v>100</v>
-      </c>
-      <c r="G26">
-        <v>87.5</v>
-      </c>
-      <c r="H26">
-        <v>100</v>
       </c>
       <c r="I26">
         <v>90</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K26">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P26">
         <v>90</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R26">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T26">
         <v>100</v>
       </c>
       <c r="U26">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="V26">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5648,13 +5493,13 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D27">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -5666,16 +5511,16 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -5687,16 +5532,16 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5708,7 +5553,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5716,13 +5561,13 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>100</v>
@@ -5737,13 +5582,13 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5758,13 +5603,13 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5784,13 +5629,13 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -5805,13 +5650,13 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -5826,13 +5671,13 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -5858,7 +5703,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -5879,7 +5724,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -5900,7 +5745,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -5926,7 +5771,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -5947,7 +5792,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5968,7 +5813,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5988,16 +5833,16 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -6009,19 +5854,19 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K32">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -6030,19 +5875,19 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R32">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -6062,10 +5907,10 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E33">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -6083,13 +5928,13 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N33">
         <v>100</v>
@@ -6104,13 +5949,13 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -6124,13 +5969,13 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -6139,7 +5984,7 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -6148,19 +5993,19 @@
         <v>90</v>
       </c>
       <c r="J34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K34">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M34">
         <v>100</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -6169,19 +6014,19 @@
         <v>90</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R34">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T34">
         <v>100</v>
       </c>
       <c r="U34">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6192,13 +6037,13 @@
         <v>44</v>
       </c>
       <c r="B35">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C35">
         <v>100</v>
       </c>
       <c r="D35">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -6213,13 +6058,13 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -6234,13 +6079,13 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6260,13 +6105,13 @@
         <v>45</v>
       </c>
       <c r="B36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>100</v>
       </c>
       <c r="D36">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>100</v>
@@ -6275,19 +6120,19 @@
         <v>100</v>
       </c>
       <c r="G36">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>100</v>
@@ -6296,19 +6141,19 @@
         <v>100</v>
       </c>
       <c r="N36">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Q36">
         <v>100</v>
       </c>
       <c r="R36">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6317,7 +6162,7 @@
         <v>100</v>
       </c>
       <c r="U36">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="V36">
         <v>100</v>
@@ -6328,134 +6173,66 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C37">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D37">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H37">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K37">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="R37">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="V37">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22">
-      <c r="A38" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38">
-        <v>80</v>
-      </c>
-      <c r="C38">
-        <v>60</v>
-      </c>
-      <c r="D38">
-        <v>17.4</v>
-      </c>
-      <c r="E38">
-        <v>40</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>25</v>
-      </c>
-      <c r="H38">
-        <v>60</v>
-      </c>
-      <c r="I38">
-        <v>80</v>
-      </c>
-      <c r="J38">
-        <v>60</v>
-      </c>
-      <c r="K38">
-        <v>17.4</v>
-      </c>
-      <c r="L38">
-        <v>40</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>25</v>
-      </c>
-      <c r="O38">
-        <v>60</v>
-      </c>
-      <c r="P38">
-        <v>80</v>
-      </c>
-      <c r="Q38">
-        <v>60</v>
-      </c>
-      <c r="R38">
-        <v>17.4</v>
-      </c>
-      <c r="S38">
-        <v>40</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>25</v>
-      </c>
-      <c r="V38">
         <v>60</v>
       </c>
     </row>
@@ -6484,31 +6261,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6516,25 +6293,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2">
-        <v>40</v>
+        <v>61.8</v>
       </c>
       <c r="G2" s="2">
-        <v>60</v>
+        <v>38.2</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6545,28 +6322,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>26</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>74.3</v>
+        <v>76.5</v>
       </c>
       <c r="G3" s="2">
-        <v>25.7</v>
+        <v>23.5</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6577,28 +6354,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>74.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25.7</v>
+        <v>20.6</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6612,31 +6389,31 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G5" s="2">
-        <v>8.6</v>
+        <v>11.8</v>
       </c>
       <c r="H5">
         <v>8.4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6644,25 +6421,25 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="G6" s="2">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6673,28 +6450,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="G7" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6705,28 +6482,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>32</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>91.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6737,10 +6514,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -6762,7 +6539,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6771,42 +6548,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920213</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6816,7 +6573,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6825,22 +6582,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6848,45 +6605,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920213</v>
+        <v>23330051920049</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920213</v>
+        <v>23330051920246</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6894,22 +6651,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920067</v>
+        <v>23330051920065</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6920,19 +6677,19 @@
         <v>23330051920067</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6940,323 +6697,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920071</v>
+        <v>23330051920072</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920071</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920072</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920072</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920074</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920074</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920057</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920246</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920061</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920062</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920064</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920259</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920065</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920066</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -906,7 +906,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -948,7 +948,7 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>9</v>
@@ -995,7 +995,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1215,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1351,7 +1351,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1440,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1482,7 +1482,7 @@
         <v>7</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1529,7 +1529,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1618,7 +1618,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1660,7 +1660,7 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1707,7 +1707,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1796,7 +1796,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1838,7 +1838,7 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -1885,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1927,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -1974,7 +1974,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2063,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2152,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2241,7 +2241,7 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2283,7 +2283,7 @@
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>9</v>
@@ -2330,7 +2330,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2419,7 +2419,7 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>7</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -2508,7 +2508,7 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2597,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2686,7 +2686,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2728,7 +2728,7 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -2775,7 +2775,7 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2817,7 +2817,7 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -2864,7 +2864,7 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2953,7 +2953,7 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2995,7 +2995,7 @@
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>9</v>
@@ -3042,7 +3042,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3131,7 +3131,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3220,7 +3220,7 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3309,7 +3309,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3351,7 +3351,7 @@
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>7</v>
@@ -3398,7 +3398,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3440,7 +3440,7 @@
         <v>5</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC33">
         <v>6</v>
@@ -3487,7 +3487,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3529,7 +3529,7 @@
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC34">
         <v>6</v>
@@ -3576,7 +3576,7 @@
         <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3618,7 +3618,7 @@
         <v>6</v>
       </c>
       <c r="AB35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC35">
         <v>10</v>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3754,7 +3754,7 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -4033,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -4054,7 +4054,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4237,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4258,7 +4258,7 @@
         <v>100</v>
       </c>
       <c r="U8">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4509,7 +4509,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4530,7 +4530,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4577,7 +4577,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4598,7 +4598,7 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4713,7 +4713,7 @@
         <v>80</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -4734,7 +4734,7 @@
         <v>80</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4781,7 +4781,7 @@
         <v>82.5</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4802,7 +4802,7 @@
         <v>82.5</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4917,7 +4917,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4938,7 +4938,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5393,7 +5393,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -5414,7 +5414,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5461,7 +5461,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O26">
         <v>90</v>
@@ -5482,7 +5482,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V26">
         <v>90</v>
@@ -5869,7 +5869,7 @@
         <v>90</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -5890,7 +5890,7 @@
         <v>90</v>
       </c>
       <c r="U32">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5937,7 +5937,7 @@
         <v>90</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5958,7 +5958,7 @@
         <v>90</v>
       </c>
       <c r="U33">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -6005,7 +6005,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -6026,7 +6026,7 @@
         <v>100</v>
       </c>
       <c r="U34">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -6073,7 +6073,7 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -6094,7 +6094,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6209,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="O37">
         <v>60</v>
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="V37">
         <v>60</v>
@@ -6471,7 +6471,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -233,6 +233,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>ARENAS</t>
   </si>
   <si>
@@ -248,6 +251,9 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>CALCANEO</t>
   </si>
   <si>
@@ -261,6 +267,9 @@
   </si>
   <si>
     <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HUGO ISAI</t>
   </si>
   <si>
     <t>YAELIS</t>
@@ -820,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -909,7 +918,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -951,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -998,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1087,7 +1096,7 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1176,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1218,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1265,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1354,7 +1363,7 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1443,7 +1452,7 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1532,7 +1541,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1621,7 +1630,7 @@
         <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1663,7 +1672,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1710,7 +1719,7 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1752,7 +1761,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1799,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1841,7 +1850,7 @@
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1888,7 +1897,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1930,7 +1939,7 @@
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1977,7 +1986,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2066,7 +2075,7 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2108,7 +2117,7 @@
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2155,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2244,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2286,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2333,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2375,7 +2384,7 @@
         <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2422,7 +2431,7 @@
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2464,7 +2473,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2511,7 +2520,7 @@
         <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2553,7 +2562,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2600,7 +2609,7 @@
         <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2689,7 +2698,7 @@
         <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2778,7 +2787,7 @@
         <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2820,7 +2829,7 @@
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2867,7 +2876,7 @@
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2956,7 +2965,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3045,7 +3054,7 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3134,7 +3143,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3223,7 +3232,7 @@
         <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3312,7 +3321,7 @@
         <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3354,7 +3363,7 @@
         <v>8</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3401,7 +3410,7 @@
         <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3443,7 +3452,7 @@
         <v>8</v>
       </c>
       <c r="AC33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3490,7 +3499,7 @@
         <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3532,7 +3541,7 @@
         <v>7</v>
       </c>
       <c r="AC34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3579,7 +3588,7 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3668,7 +3677,7 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3757,7 +3766,7 @@
         <v>5</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -4104,7 +4113,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -4125,7 +4134,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4512,7 +4521,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4533,7 +4542,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4716,7 +4725,7 @@
         <v>87.5</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P15">
         <v>85</v>
@@ -4737,7 +4746,7 @@
         <v>87.5</v>
       </c>
       <c r="V15">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4852,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="P17">
         <v>40</v>
@@ -4873,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="V17">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5124,7 +5133,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -5145,7 +5154,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5260,7 +5269,7 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -5281,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5464,7 +5473,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P26">
         <v>90</v>
@@ -5485,7 +5494,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V26">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5872,7 +5881,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P32">
         <v>90</v>
@@ -5893,7 +5902,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V32">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5940,7 +5949,7 @@
         <v>93.8</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P33">
         <v>90</v>
@@ -5961,7 +5970,7 @@
         <v>93.8</v>
       </c>
       <c r="V33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6008,7 +6017,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P34">
         <v>90</v>
@@ -6029,7 +6038,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V34">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6212,7 +6221,7 @@
         <v>12.5</v>
       </c>
       <c r="O37">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P37">
         <v>40</v>
@@ -6233,7 +6242,7 @@
         <v>12.5</v>
       </c>
       <c r="V37">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -6418,28 +6427,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C6">
         <v>34</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="G6" s="2">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6450,10 +6459,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>34</v>
@@ -6471,7 +6480,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6573,7 +6582,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6605,22 +6614,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920049</v>
+        <v>23330051920052</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6628,16 +6637,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920246</v>
+        <v>23330051920052</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6651,16 +6660,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920065</v>
+        <v>23330051920049</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -6674,16 +6683,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920067</v>
+        <v>23330051920246</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6697,16 +6706,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920072</v>
+        <v>23330051920065</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
         <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -6715,6 +6724,52 @@
         <v>60</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920067</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920072</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -233,10 +233,13 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
     <t>CERON</t>
   </si>
   <si>
-    <t>ARENAS</t>
+    <t>ESTEVEZ</t>
   </si>
   <si>
     <t>FLORES</t>
@@ -245,43 +248,37 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>CALCANEO</t>
-  </si>
-  <si>
     <t>BRAVO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
     <t>HUGO ISAI</t>
   </si>
   <si>
-    <t>YAELIS</t>
+    <t>MARY CELESTE</t>
   </si>
   <si>
     <t>LLUVIA ITZEL</t>
   </si>
   <si>
     <t>DENISSE</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
   </si>
   <si>
     <t>NATALIA</t>
@@ -832,34 +829,34 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -921,31 +918,31 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -960,7 +957,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1010,28 +1007,28 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1049,7 +1046,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1099,28 +1096,28 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1188,31 +1185,31 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1224,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
         <v>6</v>
@@ -1277,25 +1274,25 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1366,25 +1363,25 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1393,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1455,31 +1452,31 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1494,7 +1491,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1544,31 +1541,31 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1633,31 +1630,31 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1722,25 +1719,25 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1749,10 +1746,10 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -1811,46 +1808,46 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1900,43 +1897,43 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>7</v>
@@ -1989,25 +1986,25 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2078,25 +2075,25 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2105,7 +2102,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>9</v>
@@ -2167,25 +2164,25 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2206,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2256,31 +2253,31 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2295,7 +2292,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2345,25 +2342,25 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2378,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2434,25 +2431,25 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2461,13 +2458,13 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>9</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -2523,25 +2520,25 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2562,7 +2559,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2612,34 +2609,34 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2648,10 +2645,10 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2701,34 +2698,34 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>7</v>
@@ -2737,7 +2734,7 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -2790,46 +2787,46 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2879,31 +2876,31 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2918,7 +2915,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2968,25 +2965,25 @@
         <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2998,16 +2995,16 @@
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3057,37 +3054,37 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3146,25 +3143,25 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3185,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3235,25 +3232,25 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3324,25 +3321,25 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3360,10 +3357,10 @@
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3413,46 +3410,46 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>5</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3502,28 +3499,28 @@
         <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>5</v>
@@ -3532,13 +3529,13 @@
         <v>5</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC34">
         <v>7</v>
@@ -3591,25 +3588,25 @@
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3618,13 +3615,13 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z35">
         <v>9</v>
       </c>
       <c r="AA35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>10</v>
@@ -3680,25 +3677,25 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>10</v>
@@ -3769,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W37">
         <v>5</v>
@@ -3986,7 +3983,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -4048,10 +4045,10 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4060,10 +4057,10 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U5">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4134,7 +4131,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4184,22 +4181,22 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="Q7">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R7">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>70.8</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4258,16 +4255,16 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S8">
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U8">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4465,7 +4462,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4530,7 +4527,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4539,10 +4536,10 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4592,22 +4589,22 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Q13">
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S13">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T13">
         <v>100</v>
       </c>
       <c r="U13">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4728,25 +4725,25 @@
         <v>92.5</v>
       </c>
       <c r="P15">
-        <v>85</v>
+        <v>83.3</v>
       </c>
       <c r="Q15">
+        <v>91.7</v>
+      </c>
+      <c r="R15">
+        <v>93.8</v>
+      </c>
+      <c r="S15">
+        <v>93.8</v>
+      </c>
+      <c r="T15">
         <v>86.7</v>
       </c>
-      <c r="R15">
-        <v>90</v>
-      </c>
-      <c r="S15">
-        <v>90</v>
-      </c>
-      <c r="T15">
-        <v>80</v>
-      </c>
       <c r="U15">
-        <v>87.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V15">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4796,22 +4793,22 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>85</v>
+        <v>86.7</v>
       </c>
       <c r="Q16">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R16">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>82.5</v>
+        <v>88.3</v>
       </c>
       <c r="U16">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4864,10 +4861,10 @@
         <v>12.5</v>
       </c>
       <c r="P17">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="Q17">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4876,13 +4873,13 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="U17">
         <v>0</v>
       </c>
       <c r="V17">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4932,7 +4929,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4941,13 +4938,13 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -5071,7 +5068,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -5083,7 +5080,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5139,22 +5136,22 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U21">
         <v>100</v>
       </c>
       <c r="V21">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5210,16 +5207,16 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -5275,7 +5272,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5284,13 +5281,13 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5343,7 +5340,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5355,7 +5352,7 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -5408,7 +5405,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5417,13 +5414,13 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U25">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5476,25 +5473,25 @@
         <v>95</v>
       </c>
       <c r="P26">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="Q26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T26">
         <v>100</v>
       </c>
       <c r="U26">
+        <v>91.7</v>
+      </c>
+      <c r="V26">
         <v>96.90000000000001</v>
-      </c>
-      <c r="V26">
-        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5612,7 +5609,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5627,7 +5624,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5819,10 +5816,10 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="R31">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5887,22 +5884,22 @@
         <v>90</v>
       </c>
       <c r="Q32">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="R32">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S32">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="T32">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U32">
-        <v>90.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="V32">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5955,22 +5952,22 @@
         <v>90</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R33">
         <v>100</v>
       </c>
       <c r="S33">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="T33">
         <v>90</v>
       </c>
       <c r="U33">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V33">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6023,22 +6020,22 @@
         <v>90</v>
       </c>
       <c r="Q34">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T34">
         <v>100</v>
       </c>
       <c r="U34">
-        <v>96.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V34">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6088,7 +6085,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6103,7 +6100,7 @@
         <v>100</v>
       </c>
       <c r="U35">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V35">
         <v>100</v>
@@ -6224,25 +6221,25 @@
         <v>30</v>
       </c>
       <c r="P37">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="Q37">
-        <v>30</v>
+        <v>18.8</v>
       </c>
       <c r="R37">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="S37">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="T37">
         <v>0</v>
       </c>
       <c r="U37">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="V37">
-        <v>30</v>
+        <v>18.8</v>
       </c>
     </row>
   </sheetData>
@@ -6308,19 +6305,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>61.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>38.2</v>
+        <v>32.4</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6340,16 +6337,16 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="H3">
         <v>7.6</v>
@@ -6372,19 +6369,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>79.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>20.6</v>
+        <v>17.6</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6395,7 +6392,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -6404,16 +6401,16 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="G5" s="2">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5">
         <v>8.4</v>
@@ -6448,7 +6445,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6480,7 +6477,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6491,7 +6488,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -6512,7 +6509,7 @@
         <v>5.9</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6582,7 +6579,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6614,7 +6611,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920052</v>
+        <v>23330051920049</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -6623,13 +6620,13 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6637,7 +6634,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920052</v>
+        <v>23330051920049</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -6646,7 +6643,7 @@
         <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6660,7 +6657,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920049</v>
+        <v>23330051920052</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
@@ -6669,13 +6666,13 @@
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6683,16 +6680,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920246</v>
+        <v>23330051920052</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6706,22 +6703,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920065</v>
+        <v>23330051920351</v>
       </c>
       <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
         <v>74</v>
       </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6729,16 +6726,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920067</v>
+        <v>23330051920351</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6752,16 +6749,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920072</v>
+        <v>23330051920246</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -6770,6 +6767,52 @@
         <v>60</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920065</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920072</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="88">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -195,9 +198,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
@@ -643,13 +643,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AG37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -660,35 +660,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -714,77 +718,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -814,16 +830,16 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -832,16 +848,16 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -853,10 +869,10 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -865,15 +881,27 @@
         <v>9</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>9</v>
+      </c>
+      <c r="AE4">
+        <v>10</v>
+      </c>
+      <c r="AF4">
+        <v>10</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -897,72 +925,84 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>7</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD5">
+        <v>5</v>
+      </c>
+      <c r="AE5">
+        <v>7</v>
+      </c>
+      <c r="AF5">
+        <v>7</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>9</v>
@@ -989,69 +1029,81 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>8</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z6">
         <v>9</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>6</v>
+      </c>
+      <c r="AE6">
+        <v>10</v>
+      </c>
+      <c r="AF6">
+        <v>8</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -1075,58 +1127,58 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7">
         <v>1</v>
       </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P7">
+        <v>6</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+      <c r="R7">
         <v>4</v>
       </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>5</v>
+      </c>
+      <c r="T7">
         <v>0</v>
       </c>
-      <c r="S7">
-        <v>6</v>
-      </c>
-      <c r="T7">
-        <v>5</v>
-      </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>5</v>
@@ -1135,12 +1187,24 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD7">
+        <v>5</v>
+      </c>
+      <c r="AE7">
+        <v>5</v>
+      </c>
+      <c r="AF7">
+        <v>5</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -1164,72 +1228,84 @@
         <v>4</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>7</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R8">
+        <v>7</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
         <v>0</v>
       </c>
-      <c r="S8">
-        <v>8</v>
-      </c>
-      <c r="T8">
-        <v>5</v>
-      </c>
       <c r="U8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z8">
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8">
+        <v>6</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>10</v>
@@ -1265,10 +1341,10 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1277,13 +1353,13 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>10</v>
       </c>
       <c r="S9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1298,7 +1374,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1307,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -1315,10 +1391,22 @@
       <c r="AC9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AD9">
+        <v>10</v>
+      </c>
+      <c r="AE9">
+        <v>10</v>
+      </c>
+      <c r="AF9">
+        <v>10</v>
+      </c>
+      <c r="AG9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1348,66 +1436,78 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
       </c>
       <c r="S10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>10</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD10">
+        <v>6</v>
+      </c>
+      <c r="AE10">
+        <v>10</v>
+      </c>
+      <c r="AF10">
+        <v>9</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -1434,52 +1534,52 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1493,10 +1593,22 @@
       <c r="AC11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>7</v>
+      </c>
+      <c r="AE11">
+        <v>9</v>
+      </c>
+      <c r="AF11">
+        <v>9</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>8</v>
@@ -1523,52 +1635,52 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1577,15 +1689,27 @@
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12">
+        <v>7</v>
+      </c>
+      <c r="AE12">
+        <v>10</v>
+      </c>
+      <c r="AF12">
+        <v>9</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1612,69 +1736,81 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>7</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z13">
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD13">
+        <v>6</v>
+      </c>
+      <c r="AE13">
+        <v>8</v>
+      </c>
+      <c r="AF13">
+        <v>9</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -1701,69 +1837,81 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>9</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>7</v>
+      </c>
+      <c r="AE14">
+        <v>10</v>
+      </c>
+      <c r="AF14">
+        <v>9</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -1787,72 +1935,84 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>5</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V15">
+        <v>6</v>
+      </c>
+      <c r="W15">
+        <v>5</v>
+      </c>
+      <c r="X15">
         <v>4</v>
       </c>
-      <c r="W15">
-        <v>6</v>
-      </c>
-      <c r="X15">
-        <v>6</v>
-      </c>
       <c r="Y15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>6</v>
+      </c>
+      <c r="AF15">
+        <v>6</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -1876,61 +2036,61 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R16">
+        <v>6</v>
+      </c>
+      <c r="S16">
+        <v>6</v>
+      </c>
+      <c r="T16">
         <v>4</v>
       </c>
-      <c r="S16">
-        <v>7</v>
-      </c>
-      <c r="T16">
-        <v>6</v>
-      </c>
       <c r="U16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z16">
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>6</v>
@@ -1938,10 +2098,22 @@
       <c r="AC16">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:29">
+      <c r="AD16">
+        <v>5</v>
+      </c>
+      <c r="AE16">
+        <v>6</v>
+      </c>
+      <c r="AF16">
+        <v>7</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -1965,17 +2137,17 @@
         <v>4</v>
       </c>
       <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
         <v>4</v>
       </c>
-      <c r="J17">
-        <v>5</v>
-      </c>
       <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17">
         <v>0</v>
       </c>
-      <c r="L17">
-        <v>5</v>
-      </c>
       <c r="M17">
         <v>5</v>
       </c>
@@ -1983,35 +2155,35 @@
         <v>5</v>
       </c>
       <c r="O17">
+        <v>5</v>
+      </c>
+      <c r="P17">
         <v>0</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
+        <v>5</v>
+      </c>
+      <c r="R17">
         <v>3</v>
       </c>
-      <c r="Q17">
-        <v>5</v>
-      </c>
-      <c r="R17">
+      <c r="S17">
+        <v>5</v>
+      </c>
+      <c r="T17">
         <v>0</v>
       </c>
-      <c r="S17">
-        <v>5</v>
-      </c>
-      <c r="T17">
-        <v>5</v>
-      </c>
       <c r="U17">
         <v>5</v>
       </c>
       <c r="V17">
+        <v>5</v>
+      </c>
+      <c r="W17">
+        <v>5</v>
+      </c>
+      <c r="X17">
         <v>0</v>
       </c>
-      <c r="W17">
-        <v>5</v>
-      </c>
-      <c r="X17">
-        <v>5</v>
-      </c>
       <c r="Y17">
         <v>5</v>
       </c>
@@ -2027,10 +2199,22 @@
       <c r="AC17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:29">
+      <c r="AD17">
+        <v>5</v>
+      </c>
+      <c r="AE17">
+        <v>5</v>
+      </c>
+      <c r="AF17">
+        <v>5</v>
+      </c>
+      <c r="AG17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>8</v>
@@ -2057,69 +2241,81 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>10</v>
       </c>
       <c r="O18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>9</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>9</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <v>9</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC18">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:29">
+      <c r="AD18">
+        <v>9</v>
+      </c>
+      <c r="AE18">
+        <v>10</v>
+      </c>
+      <c r="AF18">
+        <v>9</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>8</v>
@@ -2146,69 +2342,81 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z19">
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
+        <v>10</v>
+      </c>
+      <c r="AF19">
+        <v>9</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>8</v>
@@ -2235,34 +2443,34 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>8</v>
       </c>
       <c r="N20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2271,19 +2479,19 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2292,12 +2500,24 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD20">
+        <v>7</v>
+      </c>
+      <c r="AE20">
+        <v>7</v>
+      </c>
+      <c r="AF20">
+        <v>7</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>8</v>
@@ -2324,19 +2544,19 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>8</v>
       </c>
       <c r="M21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -2345,48 +2565,60 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>10</v>
       </c>
       <c r="S21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD21">
+        <v>6</v>
+      </c>
+      <c r="AE21">
+        <v>10</v>
+      </c>
+      <c r="AF21">
+        <v>9</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>8</v>
@@ -2413,38 +2645,38 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>8</v>
       </c>
       <c r="M22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R22">
+        <v>10</v>
+      </c>
+      <c r="S22">
+        <v>6</v>
+      </c>
+      <c r="T22">
         <v>4</v>
       </c>
-      <c r="S22">
-        <v>9</v>
-      </c>
-      <c r="T22">
-        <v>9</v>
-      </c>
       <c r="U22">
         <v>9</v>
       </c>
@@ -2455,27 +2687,39 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>9</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:29">
+      <c r="AD22">
+        <v>8</v>
+      </c>
+      <c r="AE22">
+        <v>8</v>
+      </c>
+      <c r="AF22">
+        <v>9</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>9</v>
@@ -2502,46 +2746,46 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>9</v>
       </c>
       <c r="L23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
       </c>
       <c r="S23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>8</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2559,12 +2803,24 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD23">
+        <v>8</v>
+      </c>
+      <c r="AE23">
+        <v>10</v>
+      </c>
+      <c r="AF23">
+        <v>8</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>9</v>
@@ -2591,52 +2847,52 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>9</v>
       </c>
       <c r="P24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2645,15 +2901,27 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD24">
+        <v>6</v>
+      </c>
+      <c r="AE24">
+        <v>9</v>
+      </c>
+      <c r="AF24">
+        <v>9</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -2680,31 +2948,31 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>6</v>
@@ -2716,33 +2984,45 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD25">
+        <v>5</v>
+      </c>
+      <c r="AE25">
+        <v>7</v>
+      </c>
+      <c r="AF25">
+        <v>9</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -2766,10 +3046,10 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -2778,25 +3058,25 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P26">
+        <v>8</v>
+      </c>
+      <c r="Q26">
+        <v>10</v>
+      </c>
+      <c r="R26">
         <v>4</v>
       </c>
-      <c r="Q26">
-        <v>7</v>
-      </c>
-      <c r="R26">
-        <v>9</v>
-      </c>
       <c r="S26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2805,7 +3085,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2814,7 +3094,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>6</v>
@@ -2826,12 +3106,24 @@
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD26">
+        <v>6</v>
+      </c>
+      <c r="AE26">
+        <v>7</v>
+      </c>
+      <c r="AF26">
+        <v>7</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>9</v>
@@ -2858,69 +3150,81 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z27">
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC27">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD27">
+        <v>6</v>
+      </c>
+      <c r="AE27">
+        <v>10</v>
+      </c>
+      <c r="AF27">
+        <v>9</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>8</v>
@@ -2947,19 +3251,19 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>8</v>
@@ -2968,48 +3272,60 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>7</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:29">
+      <c r="AD28">
+        <v>6</v>
+      </c>
+      <c r="AE28">
+        <v>9</v>
+      </c>
+      <c r="AF28">
+        <v>8</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>10</v>
@@ -3036,49 +3352,49 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>9</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>10</v>
       </c>
       <c r="P29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>8</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>10</v>
@@ -3087,18 +3403,30 @@
         <v>9</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD29">
+        <v>7</v>
+      </c>
+      <c r="AE29">
+        <v>10</v>
+      </c>
+      <c r="AF29">
+        <v>10</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>9</v>
@@ -3128,40 +3456,40 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>10</v>
       </c>
       <c r="S30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>10</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3170,24 +3498,36 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC30">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD30">
+        <v>8</v>
+      </c>
+      <c r="AE30">
+        <v>10</v>
+      </c>
+      <c r="AF30">
+        <v>9</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>10</v>
@@ -3223,40 +3563,40 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>10</v>
       </c>
       <c r="S31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>10</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3265,7 +3605,7 @@
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3273,10 +3613,22 @@
       <c r="AC31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:29">
+      <c r="AD31">
+        <v>8</v>
+      </c>
+      <c r="AE31">
+        <v>10</v>
+      </c>
+      <c r="AF31">
+        <v>10</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -3300,17 +3652,17 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K32">
+        <v>5</v>
+      </c>
+      <c r="L32">
         <v>0</v>
       </c>
-      <c r="L32">
-        <v>5</v>
-      </c>
       <c r="M32">
         <v>5</v>
       </c>
@@ -3321,51 +3673,63 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC32">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD32">
+        <v>5</v>
+      </c>
+      <c r="AE32">
+        <v>7</v>
+      </c>
+      <c r="AF32">
+        <v>7</v>
+      </c>
+      <c r="AG32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -3389,40 +3753,40 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>5</v>
       </c>
       <c r="O33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S33">
         <v>5</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>5</v>
@@ -3431,30 +3795,42 @@
         <v>6</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="X33">
         <v>6</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD33">
+        <v>5</v>
+      </c>
+      <c r="AE33">
+        <v>7</v>
+      </c>
+      <c r="AF33">
+        <v>6</v>
+      </c>
+      <c r="AG33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>6</v>
@@ -3478,16 +3854,16 @@
         <v>6</v>
       </c>
       <c r="I34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3496,54 +3872,66 @@
         <v>5</v>
       </c>
       <c r="O34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>6</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD34">
+        <v>5</v>
+      </c>
+      <c r="AE34">
+        <v>6</v>
+      </c>
+      <c r="AF34">
+        <v>7</v>
+      </c>
+      <c r="AG34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -3570,69 +3958,81 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>9</v>
       </c>
       <c r="L35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
       </c>
       <c r="S35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z35">
         <v>9</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD35">
+        <v>7</v>
+      </c>
+      <c r="AE35">
+        <v>10</v>
+      </c>
+      <c r="AF35">
+        <v>10</v>
+      </c>
+      <c r="AG35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>10</v>
@@ -3718,10 +4118,22 @@
       <c r="AC36">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:29">
+      <c r="AD36">
+        <v>10</v>
+      </c>
+      <c r="AE36">
+        <v>10</v>
+      </c>
+      <c r="AF36">
+        <v>10</v>
+      </c>
+      <c r="AG36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -3745,17 +4157,17 @@
         <v>4</v>
       </c>
       <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
         <v>4</v>
       </c>
-      <c r="J37">
-        <v>5</v>
-      </c>
       <c r="K37">
+        <v>5</v>
+      </c>
+      <c r="L37">
         <v>0</v>
       </c>
-      <c r="L37">
-        <v>5</v>
-      </c>
       <c r="M37">
         <v>5</v>
       </c>
@@ -3763,35 +4175,35 @@
         <v>5</v>
       </c>
       <c r="O37">
+        <v>5</v>
+      </c>
+      <c r="P37">
         <v>0</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
+        <v>5</v>
+      </c>
+      <c r="R37">
         <v>3</v>
       </c>
-      <c r="Q37">
-        <v>5</v>
-      </c>
-      <c r="R37">
+      <c r="S37">
+        <v>5</v>
+      </c>
+      <c r="T37">
         <v>0</v>
       </c>
-      <c r="S37">
-        <v>5</v>
-      </c>
-      <c r="T37">
-        <v>5</v>
-      </c>
       <c r="U37">
         <v>5</v>
       </c>
       <c r="V37">
+        <v>5</v>
+      </c>
+      <c r="W37">
+        <v>5</v>
+      </c>
+      <c r="X37">
         <v>0</v>
       </c>
-      <c r="W37">
-        <v>5</v>
-      </c>
-      <c r="X37">
-        <v>5</v>
-      </c>
       <c r="Y37">
         <v>5</v>
       </c>
@@ -3805,15 +4217,27 @@
         <v>5</v>
       </c>
       <c r="AC37">
+        <v>5</v>
+      </c>
+      <c r="AD37">
+        <v>5</v>
+      </c>
+      <c r="AE37">
+        <v>5</v>
+      </c>
+      <c r="AF37">
+        <v>5</v>
+      </c>
+      <c r="AG37">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3821,16 +4245,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3838,26 +4262,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3883,56 +4310,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -3962,11 +4398,11 @@
         <v>100</v>
       </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
         <v>95</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
       <c r="M4">
         <v>100</v>
       </c>
@@ -3983,24 +4419,33 @@
         <v>100</v>
       </c>
       <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>96.90000000000001</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
-        <v>100</v>
-      </c>
       <c r="U4">
         <v>100</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="W4">
+        <v>100</v>
+      </c>
+      <c r="X4">
+        <v>100</v>
+      </c>
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>90</v>
@@ -4024,14 +4469,14 @@
         <v>100</v>
       </c>
       <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5">
         <v>95</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>90</v>
       </c>
-      <c r="K5">
-        <v>100</v>
-      </c>
       <c r="L5">
         <v>100</v>
       </c>
@@ -4039,36 +4484,45 @@
         <v>100</v>
       </c>
       <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
         <v>96.90000000000001</v>
       </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
       <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>93.3</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>93.8</v>
       </c>
-      <c r="R5">
-        <v>100</v>
-      </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
       <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5">
         <v>96.7</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>91.7</v>
       </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -4110,11 +4564,11 @@
         <v>100</v>
       </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>95</v>
       </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
       <c r="Q6">
         <v>100</v>
       </c>
@@ -4131,12 +4585,21 @@
         <v>100</v>
       </c>
       <c r="V6">
+        <v>100</v>
+      </c>
+      <c r="W6">
+        <v>100</v>
+      </c>
+      <c r="X6">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>80</v>
@@ -4160,17 +4623,17 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>90</v>
       </c>
       <c r="K7">
+        <v>90</v>
+      </c>
+      <c r="L7">
         <v>95</v>
       </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
       <c r="M7">
         <v>100</v>
       </c>
@@ -4181,30 +4644,39 @@
         <v>100</v>
       </c>
       <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>100</v>
+      </c>
+      <c r="R7">
         <v>86.7</v>
-      </c>
-      <c r="Q7">
-        <v>93.8</v>
-      </c>
-      <c r="R7">
-        <v>90.59999999999999</v>
       </c>
       <c r="S7">
         <v>93.8</v>
       </c>
       <c r="T7">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="U7">
+        <v>93.8</v>
+      </c>
+      <c r="V7">
         <v>96.7</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>70.8</v>
       </c>
-      <c r="V7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>80</v>
@@ -4228,51 +4700,60 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
       <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
         <v>95</v>
       </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
+        <v>100</v>
+      </c>
+      <c r="O8">
         <v>93.8</v>
       </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>90</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>100</v>
+      </c>
+      <c r="T8">
         <v>90.59999999999999</v>
       </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-      <c r="T8">
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>96.7</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>87.5</v>
       </c>
-      <c r="V8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -4337,10 +4818,19 @@
       <c r="V9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="W9">
+        <v>100</v>
+      </c>
+      <c r="X9">
+        <v>100</v>
+      </c>
+      <c r="Y9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -4405,10 +4895,19 @@
       <c r="V10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="W10">
+        <v>100</v>
+      </c>
+      <c r="X10">
+        <v>100</v>
+      </c>
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -4462,21 +4961,30 @@
         <v>100</v>
       </c>
       <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
+        <v>100</v>
+      </c>
+      <c r="U11">
         <v>93.8</v>
       </c>
-      <c r="T11">
-        <v>100</v>
-      </c>
-      <c r="U11">
-        <v>100</v>
-      </c>
       <c r="V11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11">
+        <v>100</v>
+      </c>
+      <c r="X11">
+        <v>100</v>
+      </c>
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -4506,45 +5014,54 @@
         <v>100</v>
       </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>95</v>
       </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
+        <v>100</v>
+      </c>
+      <c r="O12">
         <v>96.90000000000001</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>97.5</v>
       </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>95.3</v>
       </c>
-      <c r="S12">
-        <v>100</v>
-      </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
       <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
         <v>97.90000000000001</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>90</v>
@@ -4568,51 +5085,60 @@
         <v>100</v>
       </c>
       <c r="I13">
+        <v>100</v>
+      </c>
+      <c r="J13">
         <v>95</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
       <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>95</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>90</v>
       </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
       <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>96.90000000000001</v>
       </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>90</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>96.90000000000001</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>93.8</v>
       </c>
-      <c r="T13">
-        <v>100</v>
-      </c>
-      <c r="U13">
+      <c r="V13">
+        <v>100</v>
+      </c>
+      <c r="W13">
         <v>97.90000000000001</v>
       </c>
-      <c r="V13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="X13">
+        <v>100</v>
+      </c>
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4677,10 +5203,19 @@
       <c r="V14">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="W14">
+        <v>100</v>
+      </c>
+      <c r="X14">
+        <v>100</v>
+      </c>
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>80</v>
@@ -4704,51 +5239,60 @@
         <v>100</v>
       </c>
       <c r="I15">
+        <v>100</v>
+      </c>
+      <c r="J15">
         <v>85</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>86.7</v>
-      </c>
-      <c r="K15">
-        <v>90</v>
       </c>
       <c r="L15">
         <v>90</v>
       </c>
       <c r="M15">
+        <v>90</v>
+      </c>
+      <c r="N15">
         <v>80</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>87.5</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>92.5</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
         <v>83.3</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>91.7</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>93.8</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>93.8</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>86.7</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>85.40000000000001</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>80</v>
@@ -4772,51 +5316,60 @@
         <v>100</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>85</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>96.7</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>95</v>
       </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
       <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
         <v>82.5</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>96.90000000000001</v>
       </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
       <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>86.7</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>97.90000000000001</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>95.3</v>
       </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-      <c r="T16">
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
         <v>88.3</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>91.7</v>
       </c>
-      <c r="V16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="X16">
+        <v>100</v>
+      </c>
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>80</v>
@@ -4840,51 +5393,60 @@
         <v>25</v>
       </c>
       <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <v>40</v>
       </c>
-      <c r="J17">
-        <v>10</v>
-      </c>
       <c r="K17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
         <v>50</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>12.5</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
         <v>26.7</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>6.3</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>33.3</v>
       </c>
       <c r="U17">
         <v>0</v>
       </c>
       <c r="V17">
+        <v>33.3</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -4917,42 +5479,51 @@
         <v>100</v>
       </c>
       <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>90</v>
       </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
         <v>96.90000000000001</v>
       </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>96.7</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
       <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
         <v>93.8</v>
       </c>
-      <c r="T18">
-        <v>100</v>
-      </c>
-      <c r="U18">
+      <c r="V18">
+        <v>100</v>
+      </c>
+      <c r="W18">
         <v>97.90000000000001</v>
       </c>
-      <c r="V18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="X18">
+        <v>100</v>
+      </c>
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -5017,10 +5588,19 @@
       <c r="V19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="W19">
+        <v>100</v>
+      </c>
+      <c r="X19">
+        <v>100</v>
+      </c>
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -5068,27 +5648,36 @@
         <v>100</v>
       </c>
       <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
         <v>93.8</v>
       </c>
-      <c r="R20">
-        <v>100</v>
-      </c>
-      <c r="S20">
-        <v>100</v>
-      </c>
       <c r="T20">
         <v>100</v>
       </c>
       <c r="U20">
+        <v>100</v>
+      </c>
+      <c r="V20">
+        <v>100</v>
+      </c>
+      <c r="W20">
         <v>93.8</v>
       </c>
-      <c r="V20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="X20">
+        <v>100</v>
+      </c>
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -5115,11 +5704,11 @@
         <v>100</v>
       </c>
       <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>90</v>
       </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
       <c r="L21">
         <v>100</v>
       </c>
@@ -5130,13 +5719,13 @@
         <v>100</v>
       </c>
       <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21">
         <v>90</v>
       </c>
-      <c r="P21">
-        <v>100</v>
-      </c>
       <c r="Q21">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5145,18 +5734,27 @@
         <v>93.8</v>
       </c>
       <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>93.8</v>
+      </c>
+      <c r="V21">
         <v>96.7</v>
       </c>
-      <c r="U21">
-        <v>100</v>
-      </c>
-      <c r="V21">
+      <c r="W21">
+        <v>100</v>
+      </c>
+      <c r="X21">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -5207,24 +5805,33 @@
         <v>100</v>
       </c>
       <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>96.90000000000001</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
         <v>96.7</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>97.90000000000001</v>
       </c>
-      <c r="V22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="X22">
+        <v>100</v>
+      </c>
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -5251,11 +5858,11 @@
         <v>100</v>
       </c>
       <c r="J23">
+        <v>100</v>
+      </c>
+      <c r="K23">
         <v>90</v>
       </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
       <c r="L23">
         <v>100</v>
       </c>
@@ -5266,33 +5873,42 @@
         <v>100</v>
       </c>
       <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="P23">
         <v>95</v>
       </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
       <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
         <v>93.8</v>
       </c>
-      <c r="R23">
-        <v>100</v>
-      </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
       <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
+        <v>100</v>
+      </c>
+      <c r="V23">
         <v>98.3</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>97.90000000000001</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Y23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -5319,11 +5935,11 @@
         <v>100</v>
       </c>
       <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>90</v>
       </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
       <c r="L24">
         <v>100</v>
       </c>
@@ -5340,27 +5956,36 @@
         <v>100</v>
       </c>
       <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
         <v>93.8</v>
       </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
-      <c r="S24">
-        <v>100</v>
-      </c>
       <c r="T24">
         <v>100</v>
       </c>
       <c r="U24">
+        <v>100</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+      <c r="W24">
         <v>97.90000000000001</v>
       </c>
-      <c r="V24">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="X24">
+        <v>100</v>
+      </c>
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>90</v>
@@ -5384,51 +6009,60 @@
         <v>100</v>
       </c>
       <c r="I25">
+        <v>100</v>
+      </c>
+      <c r="J25">
         <v>95</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
         <v>90</v>
       </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
       <c r="N25">
+        <v>100</v>
+      </c>
+      <c r="O25">
         <v>93.8</v>
       </c>
-      <c r="O25">
-        <v>100</v>
-      </c>
       <c r="P25">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>96.7</v>
       </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
-        <v>100</v>
-      </c>
       <c r="S25">
+        <v>100</v>
+      </c>
+      <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
         <v>93.8</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>98.3</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>89.59999999999999</v>
       </c>
-      <c r="V25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="X25">
+        <v>100</v>
+      </c>
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>80</v>
@@ -5452,34 +6086,34 @@
         <v>90</v>
       </c>
       <c r="I26">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>90</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
         <v>90</v>
       </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
       <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
         <v>96.90000000000001</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>95</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>93.3</v>
-      </c>
-      <c r="Q26">
-        <v>93.8</v>
-      </c>
-      <c r="R26">
-        <v>100</v>
       </c>
       <c r="S26">
         <v>93.8</v>
@@ -5488,15 +6122,24 @@
         <v>100</v>
       </c>
       <c r="U26">
+        <v>93.8</v>
+      </c>
+      <c r="V26">
+        <v>100</v>
+      </c>
+      <c r="W26">
         <v>91.7</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -5561,10 +6204,19 @@
       <c r="V27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="W27">
+        <v>100</v>
+      </c>
+      <c r="X27">
+        <v>100</v>
+      </c>
+      <c r="Y27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>90</v>
@@ -5588,11 +6240,11 @@
         <v>100</v>
       </c>
       <c r="I28">
+        <v>100</v>
+      </c>
+      <c r="J28">
         <v>95</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
       <c r="K28">
         <v>100</v>
       </c>
@@ -5609,14 +6261,14 @@
         <v>100</v>
       </c>
       <c r="P28">
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>96.7</v>
       </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
-        <v>100</v>
-      </c>
       <c r="S28">
         <v>100</v>
       </c>
@@ -5624,15 +6276,24 @@
         <v>100</v>
       </c>
       <c r="U28">
+        <v>100</v>
+      </c>
+      <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
         <v>97.90000000000001</v>
       </c>
-      <c r="V28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="X28">
+        <v>100</v>
+      </c>
+      <c r="Y28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -5697,10 +6358,19 @@
       <c r="V29">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="W29">
+        <v>100</v>
+      </c>
+      <c r="X29">
+        <v>100</v>
+      </c>
+      <c r="Y29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -5765,10 +6435,19 @@
       <c r="V30">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="W30">
+        <v>100</v>
+      </c>
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -5798,11 +6477,11 @@
         <v>100</v>
       </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>95</v>
       </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
       <c r="M31">
         <v>100</v>
       </c>
@@ -5816,27 +6495,36 @@
         <v>100</v>
       </c>
       <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
         <v>95.8</v>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>96.90000000000001</v>
       </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
-        <v>100</v>
-      </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="W31">
+        <v>100</v>
+      </c>
+      <c r="X31">
+        <v>100</v>
+      </c>
+      <c r="Y31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>90</v>
@@ -5860,51 +6548,60 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J32">
         <v>90</v>
       </c>
       <c r="K32">
+        <v>90</v>
+      </c>
+      <c r="L32">
         <v>95</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>80</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>90</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>90.59999999999999</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>92.5</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
         <v>90</v>
-      </c>
-      <c r="Q32">
-        <v>87.5</v>
-      </c>
-      <c r="R32">
-        <v>93.8</v>
       </c>
       <c r="S32">
         <v>87.5</v>
       </c>
       <c r="T32">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="U32">
         <v>87.5</v>
       </c>
       <c r="V32">
+        <v>93.3</v>
+      </c>
+      <c r="W32">
+        <v>87.5</v>
+      </c>
+      <c r="X32">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="Y32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>90</v>
@@ -5928,51 +6625,60 @@
         <v>100</v>
       </c>
       <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
         <v>90</v>
       </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>90</v>
       </c>
       <c r="N33">
+        <v>90</v>
+      </c>
+      <c r="O33">
         <v>93.8</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>97.5</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>90</v>
       </c>
-      <c r="Q33">
+      <c r="S33">
         <v>93.8</v>
       </c>
-      <c r="R33">
-        <v>100</v>
-      </c>
-      <c r="S33">
+      <c r="T33">
+        <v>100</v>
+      </c>
+      <c r="U33">
         <v>87.5</v>
       </c>
-      <c r="T33">
+      <c r="V33">
         <v>90</v>
       </c>
-      <c r="U33">
+      <c r="W33">
         <v>89.59999999999999</v>
       </c>
-      <c r="V33">
+      <c r="X33">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="34" spans="1:22">
+      <c r="Y33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
       <c r="A34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34">
         <v>80</v>
@@ -5996,51 +6702,60 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J34">
         <v>90</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L34">
+        <v>100</v>
+      </c>
+      <c r="M34">
         <v>90</v>
       </c>
-      <c r="M34">
-        <v>100</v>
-      </c>
       <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
         <v>96.90000000000001</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>97.5</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
+        <v>100</v>
+      </c>
+      <c r="R34">
         <v>90</v>
       </c>
-      <c r="Q34">
+      <c r="S34">
         <v>87.5</v>
       </c>
-      <c r="R34">
-        <v>100</v>
-      </c>
-      <c r="S34">
+      <c r="T34">
+        <v>100</v>
+      </c>
+      <c r="U34">
         <v>93.8</v>
       </c>
-      <c r="T34">
-        <v>100</v>
-      </c>
-      <c r="U34">
+      <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
         <v>91.7</v>
       </c>
-      <c r="V34">
+      <c r="X34">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="35" spans="1:22">
+      <c r="Y34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
       <c r="A35" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35">
         <v>90</v>
@@ -6064,11 +6779,11 @@
         <v>100</v>
       </c>
       <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
         <v>95</v>
       </c>
-      <c r="J35">
-        <v>100</v>
-      </c>
       <c r="K35">
         <v>100</v>
       </c>
@@ -6079,20 +6794,20 @@
         <v>100</v>
       </c>
       <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
         <v>96.90000000000001</v>
       </c>
-      <c r="O35">
-        <v>100</v>
-      </c>
       <c r="P35">
+        <v>100</v>
+      </c>
+      <c r="Q35">
+        <v>100</v>
+      </c>
+      <c r="R35">
         <v>96.7</v>
       </c>
-      <c r="Q35">
-        <v>100</v>
-      </c>
-      <c r="R35">
-        <v>100</v>
-      </c>
       <c r="S35">
         <v>100</v>
       </c>
@@ -6100,15 +6815,24 @@
         <v>100</v>
       </c>
       <c r="U35">
+        <v>100</v>
+      </c>
+      <c r="V35">
+        <v>100</v>
+      </c>
+      <c r="W35">
         <v>97.90000000000001</v>
       </c>
-      <c r="V35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22">
+      <c r="X35">
+        <v>100</v>
+      </c>
+      <c r="Y35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
       <c r="A36" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>100</v>
@@ -6173,10 +6897,19 @@
       <c r="V36">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:22">
+      <c r="W36">
+        <v>100</v>
+      </c>
+      <c r="X36">
+        <v>100</v>
+      </c>
+      <c r="Y36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
       <c r="A37" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37">
         <v>80</v>
@@ -6200,53 +6933,62 @@
         <v>60</v>
       </c>
       <c r="I37">
+        <v>20</v>
+      </c>
+      <c r="J37">
         <v>40</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>30</v>
       </c>
-      <c r="K37">
-        <v>10</v>
-      </c>
       <c r="L37">
+        <v>10</v>
+      </c>
+      <c r="M37">
         <v>20</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>0</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>12.5</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>30</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
+        <v>10</v>
+      </c>
+      <c r="R37">
         <v>26.7</v>
       </c>
-      <c r="Q37">
+      <c r="S37">
         <v>18.8</v>
       </c>
-      <c r="R37">
+      <c r="T37">
         <v>6.3</v>
       </c>
-      <c r="S37">
+      <c r="U37">
         <v>12.5</v>
       </c>
-      <c r="T37">
+      <c r="V37">
         <v>0</v>
       </c>
-      <c r="U37">
+      <c r="W37">
         <v>8.300000000000001</v>
       </c>
-      <c r="V37">
+      <c r="X37">
         <v>18.8</v>
+      </c>
+      <c r="Y37">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6267,31 +7009,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -6520,21 +7262,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>66</v>
       </c>
       <c r="C9">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="H9">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6569,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6603,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -878,16 +878,16 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>10</v>
       </c>
       <c r="AD4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE4">
         <v>10</v>
@@ -976,25 +976,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA5">
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1077,25 +1077,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE6">
         <v>10</v>
       </c>
       <c r="AF6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1187,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD7">
         <v>5</v>
@@ -1279,25 +1279,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -1481,25 +1481,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>10</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10">
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1582,25 +1582,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1683,25 +1683,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE12">
         <v>10</v>
       </c>
       <c r="AF12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1784,25 +1784,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1888,22 +1888,22 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE14">
         <v>10</v>
       </c>
       <c r="AF14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1986,25 +1986,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB15">
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD15">
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2087,25 +2087,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD16">
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2289,25 +2289,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE18">
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2390,25 +2390,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
         <v>10</v>
       </c>
       <c r="AF19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2491,25 +2491,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2592,25 +2592,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE21">
         <v>10</v>
       </c>
       <c r="AF21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2693,25 +2693,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2797,7 +2797,7 @@
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB23">
         <v>10</v>
@@ -2806,13 +2806,13 @@
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE23">
         <v>10</v>
       </c>
       <c r="AF23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -2898,22 +2898,22 @@
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>10</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -2996,25 +2996,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD25">
         <v>5</v>
       </c>
       <c r="AE25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3097,25 +3097,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3201,22 +3201,22 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC27">
         <v>10</v>
       </c>
       <c r="AD27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE27">
         <v>10</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3299,25 +3299,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3400,19 +3400,19 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB29">
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE29">
         <v>10</v>
@@ -3504,22 +3504,22 @@
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC30">
         <v>10</v>
       </c>
       <c r="AD30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3605,7 +3605,7 @@
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3614,7 +3614,7 @@
         <v>10</v>
       </c>
       <c r="AD31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE31">
         <v>10</v>
@@ -3703,7 +3703,7 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA32">
         <v>5</v>
@@ -3712,16 +3712,16 @@
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3804,25 +3804,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD33">
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3905,7 +3905,7 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -3914,16 +3914,16 @@
         <v>5</v>
       </c>
       <c r="AC34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD34">
         <v>5</v>
       </c>
       <c r="AE34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -4006,19 +4006,19 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE35">
         <v>10</v>
@@ -7059,7 +7059,7 @@
         <v>32.4</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7091,7 +7091,7 @@
         <v>20.6</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7123,7 +7123,7 @@
         <v>17.6</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7219,7 +7219,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>5.9</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/1CM - Estadisticos 20231.xlsx
+++ b/grupos/1CM - Estadisticos 20231.xlsx
@@ -878,16 +878,16 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>10</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE4">
         <v>10</v>
@@ -976,25 +976,25 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD5">
         <v>5</v>
       </c>
       <c r="AE5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1077,25 +1077,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE6">
         <v>10</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1187,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD7">
         <v>5</v>
@@ -1279,25 +1279,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB8">
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
@@ -1481,25 +1481,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>10</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE10">
         <v>10</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1582,25 +1582,25 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1683,25 +1683,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE12">
         <v>10</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1784,25 +1784,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1888,22 +1888,22 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE14">
         <v>10</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1986,25 +1986,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD15">
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2087,25 +2087,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD16">
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2289,25 +2289,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE18">
         <v>10</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2390,25 +2390,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
         <v>10</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2491,25 +2491,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2592,25 +2592,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE21">
         <v>10</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2693,25 +2693,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2797,7 +2797,7 @@
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>10</v>
@@ -2806,13 +2806,13 @@
         <v>10</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE23">
         <v>10</v>
       </c>
       <c r="AF23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG23">
         <v>10</v>
@@ -2898,22 +2898,22 @@
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>10</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -2996,25 +2996,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD25">
         <v>5</v>
       </c>
       <c r="AE25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3097,25 +3097,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3201,22 +3201,22 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>10</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE27">
         <v>10</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3299,25 +3299,25 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3400,19 +3400,19 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE29">
         <v>10</v>
@@ -3504,22 +3504,22 @@
         <v>10</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>10</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE30">
         <v>10</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3605,7 +3605,7 @@
         <v>10</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3614,7 +3614,7 @@
         <v>10</v>
       </c>
       <c r="AD31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE31">
         <v>10</v>
@@ -3703,7 +3703,7 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>5</v>
@@ -3712,16 +3712,16 @@
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3804,25 +3804,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD33">
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3905,7 +3905,7 @@
         <v>10</v>
       </c>
       <c r="Z34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>5</v>
@@ -3914,16 +3914,16 @@
         <v>5</v>
       </c>
       <c r="AC34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD34">
         <v>5</v>
       </c>
       <c r="AE34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -4006,19 +4006,19 @@
         <v>10</v>
       </c>
       <c r="Z35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE35">
         <v>10</v>
@@ -7059,7 +7059,7 @@
         <v>32.4</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7091,7 +7091,7 @@
         <v>20.6</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7123,7 +7123,7 @@
         <v>17.6</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7219,7 +7219,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7251,7 +7251,7 @@
         <v>5.9</v>
       </c>
       <c r="H8">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
